--- a/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
+++ b/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>07/15 18:20:02</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>13173</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>110000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>13173.65</t>
+          <t>110000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13173.65</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>13173</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>13173.65</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.65</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
+++ b/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
@@ -75,210 +75,252 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>07/17 15:25:54</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.35</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>11976.05</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>07/15 16:22:47</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>110000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.35</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>13173.65</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>标记人</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>07/15 18:20:02</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>13173</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>110000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>13173.65</t>
+          <t>210000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>13173</t>
+          <t>25149.7</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>13173</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.65</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>11976.7</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
+++ b/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
@@ -244,83 +244,110 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>07/17 17:15:59</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>11976</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>07/15 18:20:02</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>13173</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>210000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>25149.7</t>
+          <t>210000</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>13173</t>
+          <t>25149.7</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>25149</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>11976.7</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0.7</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
+++ b/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/17 15:25:54</t>
+          <t>07/20 14:00:36</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11976.05</t>
+          <t>7142.86</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,237 +117,279 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>07/17 15:25:54</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8.35</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>11976.05</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>07/15 16:22:47</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>110000</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>8.35</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>13173.65</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/17 17:15:59</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>07/17 17:15:59</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>11976</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>07/15 18:20:02</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>13173</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>210000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>25149.7</t>
+          <t>270000</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>25149</t>
+          <t>32292.56</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>25149</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>0.7</t>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>7143.56</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
+++ b/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
@@ -286,12 +286,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/17 17:15:59</t>
+          <t>07/20 14:00:54</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -313,83 +313,110 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>07/17 17:15:59</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>11976</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>07/15 18:20:02</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>13173</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>270000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>32292.56</t>
+          <t>270000</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>25149</t>
+          <t>32292.56</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>25537</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>7143.56</t>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>6755.56</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
+++ b/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
@@ -286,12 +286,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/20 14:00:54</t>
+          <t>07/20 15:05:00</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>6754</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -313,12 +313,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/17 17:15:59</t>
+          <t>07/20 14:00:54</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -340,83 +340,110 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>07/17 17:15:59</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>11976</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>07/15 18:20:02</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>13173</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>270000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>32292.56</t>
+          <t>270000</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>25537</t>
+          <t>32292.56</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>32291</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>6755.56</t>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1.56</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
+++ b/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/20 14:00:36</t>
+          <t>07/22 10:21:23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>7142.86</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/17 15:25:54</t>
+          <t>07/20 14:00:36</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>11976.05</t>
+          <t>7142.86</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,166 +159,181 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>07/17 15:25:54</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>8.35</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>11976.05</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>07/15 16:22:47</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>110000</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>8.35</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>13173.65</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/20 15:05:00</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/20 14:00:54</t>
+          <t>07/20 15:05:00</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>6754</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -340,12 +355,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/17 17:15:59</t>
+          <t>07/20 14:00:54</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -367,83 +382,110 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>07/17 17:15:59</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>11976</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>07/15 18:20:02</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>13173</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>270000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>32292.56</t>
+          <t>470000</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>32291</t>
+          <t>56388.94</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>32291</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1.56</t>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>24097.94</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
+++ b/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
@@ -328,12 +328,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/20 15:05:00</t>
+          <t>07/22 14:19:28</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -355,12 +355,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/20 14:00:54</t>
+          <t>07/20 15:05:00</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>6754</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -382,12 +382,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/17 17:15:59</t>
+          <t>07/20 14:00:54</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -409,83 +409,110 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>07/17 17:15:59</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>11976</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>07/15 18:20:02</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>13173</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>470000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>56388.94</t>
+          <t>470000</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>32291</t>
+          <t>56388.94</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>56387</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>24097.94</t>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1.94</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
+++ b/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/22 10:21:23</t>
+          <t>07/23 10:05:11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>48780.49</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/20 14:00:36</t>
+          <t>07/22 10:21:23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>7142.86</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/17 15:25:54</t>
+          <t>07/20 14:00:36</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>11976.05</t>
+          <t>7142.86</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,166 +201,181 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>07/17 15:25:54</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>8.35</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>11976.05</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>07/15 16:22:47</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>110000</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>8.35</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>13173.65</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/22 14:19:28</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/20 15:05:00</t>
+          <t>07/22 14:19:28</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -382,12 +397,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/20 14:00:54</t>
+          <t>07/20 15:05:00</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>6754</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -409,12 +424,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/17 17:15:59</t>
+          <t>07/20 14:00:54</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -436,83 +451,110 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>07/17 17:15:59</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>11976</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>07/15 18:20:02</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>13173</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>470000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>56388.94</t>
+          <t>870000</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>56387</t>
+          <t>105169.43</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>56387</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>1.94</t>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>48782.43</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
+++ b/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/23 10:05:11</t>
+          <t>07/23 10:46:53</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>48780.49</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/22 10:21:23</t>
+          <t>07/23 10:05:11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>48780.49</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/20 14:00:36</t>
+          <t>07/22 10:21:23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>7142.86</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/17 15:25:54</t>
+          <t>07/20 14:00:36</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>11976.05</t>
+          <t>7142.86</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,166 +243,181 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>07/17 15:25:54</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>8.35</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>11976.05</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>07/15 16:22:47</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>110000</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>8.35</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>13173.65</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/22 14:19:28</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/20 15:05:00</t>
+          <t>07/22 14:19:28</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -424,12 +439,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/20 14:00:54</t>
+          <t>07/20 15:05:00</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>6754</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -451,12 +466,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/17 17:15:59</t>
+          <t>07/20 14:00:54</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -478,83 +493,110 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>07/17 17:15:59</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>11976</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>07/15 18:20:02</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>13173</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>870000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>105169.43</t>
+          <t>1120000</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>56387</t>
+          <t>135289.91</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>56387</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>48782.43</t>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>78902.91</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
+++ b/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
@@ -412,12 +412,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/22 14:19:28</t>
+          <t>07/23 12:17:40</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>78900</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -439,12 +439,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/20 15:05:00</t>
+          <t>07/22 14:19:28</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -466,12 +466,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/20 14:00:54</t>
+          <t>07/20 15:05:00</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>6754</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -493,12 +493,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/17 17:15:59</t>
+          <t>07/20 14:00:54</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -520,83 +520,110 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>07/17 17:15:59</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>11976</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>07/15 18:20:02</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>13173</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>1120000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>135289.91</t>
+          <t>1120000</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>56387</t>
+          <t>135289.91</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>135287</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>78902.91</t>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2.91</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
+++ b/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/23 10:46:53</t>
+          <t>07/24 10:07:41</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>15294.12</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/23 10:05:11</t>
+          <t>07/23 10:46:53</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>48780.49</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/22 10:21:23</t>
+          <t>07/23 10:05:11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>48780.49</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/20 14:00:36</t>
+          <t>07/22 10:21:23</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>7142.86</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/17 15:25:54</t>
+          <t>07/20 14:00:36</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>11976.05</t>
+          <t>7142.86</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,166 +285,181 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>07/17 15:25:54</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>8.35</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>11976.05</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>07/15 16:22:47</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>110000</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>8.35</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>13173.65</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="F11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/23 12:17:40</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>78900</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/22 14:19:28</t>
+          <t>07/23 12:17:40</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>78900</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -466,12 +481,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/20 15:05:00</t>
+          <t>07/22 14:19:28</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -493,12 +508,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/20 14:00:54</t>
+          <t>07/20 15:05:00</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>6754</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -520,12 +535,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/17 17:15:59</t>
+          <t>07/20 14:00:54</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -547,83 +562,110 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>07/17 17:15:59</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>11976</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>07/15 18:20:02</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>13173</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>1120000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>135289.91</t>
+          <t>1250000</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>135287</t>
+          <t>150584.03</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>135287</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2.91</t>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>15297.03</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
+++ b/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
@@ -454,12 +454,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/23 12:17:40</t>
+          <t>07/24 10:07:46</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>78900</t>
+          <t>588</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -469,7 +469,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -481,12 +481,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/22 14:19:28</t>
+          <t>07/23 12:17:40</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>78900</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -508,12 +508,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/20 15:05:00</t>
+          <t>07/22 14:19:28</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -535,12 +535,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/20 14:00:54</t>
+          <t>07/20 15:05:00</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>6754</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -562,12 +562,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/17 17:15:59</t>
+          <t>07/20 14:00:54</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -589,83 +589,110 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>07/17 17:15:59</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>11976</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>07/15 18:20:02</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>13173</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>1250000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>150584.03</t>
+          <t>1250000</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>135287</t>
+          <t>150584.03</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>135875</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>15297.03</t>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>14709.03</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
+++ b/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
@@ -454,12 +454,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/24 10:07:46</t>
+          <t>07/24 12:14:27</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>14706</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -469,7 +469,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -481,12 +481,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/23 12:17:40</t>
+          <t>07/24 10:07:46</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>78900</t>
+          <t>588</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -496,7 +496,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -508,12 +508,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/22 14:19:28</t>
+          <t>07/23 12:17:40</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>78900</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -535,12 +535,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/20 15:05:00</t>
+          <t>07/22 14:19:28</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -562,12 +562,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/20 14:00:54</t>
+          <t>07/20 15:05:00</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>6754</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -589,12 +589,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/17 17:15:59</t>
+          <t>07/20 14:00:54</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -616,83 +616,110 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>07/17 17:15:59</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>11976</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>07/15 18:20:02</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>13173</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>1250000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>150584.03</t>
+          <t>1250000</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>135875</t>
+          <t>150584.03</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>150581</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>14709.03</t>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>3.03</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
+++ b/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/24 10:07:41</t>
+          <t>07/27 10:22:47</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>290000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>15294.12</t>
+          <t>34939.76</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/23 10:46:53</t>
+          <t>07/24 10:07:41</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>15294.12</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/23 10:05:11</t>
+          <t>07/23 10:46:53</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>48780.49</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/22 10:21:23</t>
+          <t>07/23 10:05:11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>48780.49</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/20 14:00:36</t>
+          <t>07/22 10:21:23</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>7142.86</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/17 15:25:54</t>
+          <t>07/20 14:00:36</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>11976.05</t>
+          <t>7142.86</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,166 +327,181 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>07/17 15:25:54</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>8.35</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>11976.05</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>07/15 16:22:47</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>110000</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>8.35</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>13173.65</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="F12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/24 12:14:27</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14706</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/24 10:07:46</t>
+          <t>07/24 12:14:27</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>14706</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -496,7 +511,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -508,12 +523,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/23 12:17:40</t>
+          <t>07/24 10:07:46</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>78900</t>
+          <t>588</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -523,7 +538,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -535,12 +550,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/22 14:19:28</t>
+          <t>07/23 12:17:40</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>78900</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -562,12 +577,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/20 15:05:00</t>
+          <t>07/22 14:19:28</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -589,12 +604,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/20 14:00:54</t>
+          <t>07/20 15:05:00</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>6754</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -616,12 +631,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/17 17:15:59</t>
+          <t>07/20 14:00:54</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -643,83 +658,110 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>07/17 17:15:59</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>11976</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>07/15 18:20:02</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>13173</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>1250000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>150584.03</t>
+          <t>1540000</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>150581</t>
+          <t>185523.79</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>150581</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>3.03</t>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>34942.79</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
+++ b/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
@@ -496,12 +496,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/24 12:14:27</t>
+          <t>07/27 12:33:27</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14706</t>
+          <t>34939</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -523,12 +523,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/24 10:07:46</t>
+          <t>07/24 12:14:27</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>14706</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -550,12 +550,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/23 12:17:40</t>
+          <t>07/24 10:07:46</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>78900</t>
+          <t>588</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -577,12 +577,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/22 14:19:28</t>
+          <t>07/23 12:17:40</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>78900</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -604,12 +604,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/20 15:05:00</t>
+          <t>07/22 14:19:28</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -631,12 +631,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/20 14:00:54</t>
+          <t>07/20 15:05:00</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>6754</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -658,12 +658,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/17 17:15:59</t>
+          <t>07/20 14:00:54</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -685,83 +685,110 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>07/17 17:15:59</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>11976</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>07/15 18:20:02</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>13173</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>1540000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>185523.79</t>
+          <t>1540000</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>150581</t>
+          <t>185523.79</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>185520</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>34942.79</t>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>3.79</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
+++ b/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/27 10:22:47</t>
+          <t>07/31 14:44:37</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>290000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>34939.76</t>
+          <t>20359.28</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/24 10:07:41</t>
+          <t>07/27 10:22:47</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>290000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>15294.12</t>
+          <t>34939.76</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/23 10:46:53</t>
+          <t>07/24 10:07:41</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>15294.12</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/23 10:05:11</t>
+          <t>07/23 10:46:53</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>48780.49</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/22 10:21:23</t>
+          <t>07/23 10:05:11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>48780.49</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/20 14:00:36</t>
+          <t>07/22 10:21:23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>7142.86</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/17 15:25:54</t>
+          <t>07/20 14:00:36</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>11976.05</t>
+          <t>7142.86</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,166 +369,181 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>07/17 15:25:54</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>8.35</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>11976.05</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>07/15 16:22:47</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>110000</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>8.35</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>13173.65</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
+      <c r="F13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/27 12:33:27</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>34939</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/24 12:14:27</t>
+          <t>07/27 12:33:27</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14706</t>
+          <t>34939</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -550,12 +565,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/24 10:07:46</t>
+          <t>07/24 12:14:27</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>14706</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -565,7 +580,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -577,12 +592,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/23 12:17:40</t>
+          <t>07/24 10:07:46</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>78900</t>
+          <t>588</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -592,7 +607,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -604,12 +619,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/22 14:19:28</t>
+          <t>07/23 12:17:40</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>78900</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -631,12 +646,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/20 15:05:00</t>
+          <t>07/22 14:19:28</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -658,12 +673,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/20 14:00:54</t>
+          <t>07/20 15:05:00</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>6754</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -685,12 +700,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/17 17:15:59</t>
+          <t>07/20 14:00:54</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -712,83 +727,110 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>07/17 17:15:59</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>11976</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>07/15 18:20:02</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>13173</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>1540000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>185523.79</t>
+          <t>1710000</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>185520</t>
+          <t>205883.07</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>185520</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>3.79</t>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>20363.07</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
+++ b/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/31 14:44:37</t>
+          <t>07/31 14:56:13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>350000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20359.28</t>
+          <t>42424.24</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/27 10:22:47</t>
+          <t>07/31 14:44:37</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>290000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>34939.76</t>
+          <t>20359.28</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/24 10:07:41</t>
+          <t>07/27 10:22:47</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>290000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>15294.12</t>
+          <t>34939.76</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/23 10:46:53</t>
+          <t>07/24 10:07:41</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>15294.12</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/23 10:05:11</t>
+          <t>07/23 10:46:53</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>48780.49</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/22 10:21:23</t>
+          <t>07/23 10:05:11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>48780.49</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/20 14:00:36</t>
+          <t>07/22 10:21:23</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>7142.86</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/17 15:25:54</t>
+          <t>07/20 14:00:36</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>11976.05</t>
+          <t>7142.86</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,166 +411,181 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>07/17 15:25:54</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>8.35</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>11976.05</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>07/15 16:22:47</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>110000</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>8.35</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>13173.65</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="F14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/27 12:33:27</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>34939</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/24 12:14:27</t>
+          <t>07/27 12:33:27</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>14706</t>
+          <t>34939</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -592,12 +607,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/24 10:07:46</t>
+          <t>07/24 12:14:27</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>14706</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -607,7 +622,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -619,12 +634,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/23 12:17:40</t>
+          <t>07/24 10:07:46</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>78900</t>
+          <t>588</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -634,7 +649,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -646,12 +661,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/22 14:19:28</t>
+          <t>07/23 12:17:40</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>78900</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -673,12 +688,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/20 15:05:00</t>
+          <t>07/22 14:19:28</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -700,12 +715,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/20 14:00:54</t>
+          <t>07/20 15:05:00</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>6754</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -727,12 +742,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/17 17:15:59</t>
+          <t>07/20 14:00:54</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -754,83 +769,110 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>07/17 17:15:59</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>11976</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>07/15 18:20:02</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>13173</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>1710000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>205883.07</t>
+          <t>2060000</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>185520</t>
+          <t>248307.31</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>185520</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>20363.07</t>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>62787.31</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
+++ b/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
@@ -580,12 +580,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/27 12:33:27</t>
+          <t>07/31 16:18:51</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>34939</t>
+          <t>62783</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -607,12 +607,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/24 12:14:27</t>
+          <t>07/27 12:33:27</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>14706</t>
+          <t>34939</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -634,12 +634,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/24 10:07:46</t>
+          <t>07/24 12:14:27</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>14706</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -661,12 +661,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/23 12:17:40</t>
+          <t>07/24 10:07:46</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>78900</t>
+          <t>588</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -688,12 +688,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/22 14:19:28</t>
+          <t>07/23 12:17:40</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>78900</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -715,12 +715,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/20 15:05:00</t>
+          <t>07/22 14:19:28</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -742,12 +742,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/20 14:00:54</t>
+          <t>07/20 15:05:00</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>6754</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -769,12 +769,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/17 17:15:59</t>
+          <t>07/20 14:00:54</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -796,83 +796,110 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>07/17 17:15:59</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>11976</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>07/15 18:20:02</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>13173</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2060000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>248307.31</t>
+          <t>2060000</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>185520</t>
+          <t>248307.31</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>248303</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>62787.31</t>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>4.31</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
+++ b/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/31 14:56:13</t>
+          <t>07/31 20:06:51</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>350000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>42424.24</t>
+          <t>17964.07</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/31 14:44:37</t>
+          <t>07/31 14:56:13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>350000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20359.28</t>
+          <t>42424.24</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/27 10:22:47</t>
+          <t>07/31 14:44:37</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>290000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>34939.76</t>
+          <t>20359.28</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/24 10:07:41</t>
+          <t>07/27 10:22:47</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>290000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>15294.12</t>
+          <t>34939.76</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/23 10:46:53</t>
+          <t>07/24 10:07:41</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>15294.12</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/23 10:05:11</t>
+          <t>07/23 10:46:53</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>48780.49</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/22 10:21:23</t>
+          <t>07/23 10:05:11</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>48780.49</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/20 14:00:36</t>
+          <t>07/22 10:21:23</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>7142.86</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/17 15:25:54</t>
+          <t>07/20 14:00:36</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>11976.05</t>
+          <t>7142.86</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,166 +453,181 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>07/17 15:25:54</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>8.35</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>11976.05</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>07/15 16:22:47</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>110000</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>8.35</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>13173.65</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
+      <c r="F15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/31 16:18:51</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>62783</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/27 12:33:27</t>
+          <t>07/31 16:18:51</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>34939</t>
+          <t>62783</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -622,7 +637,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -634,12 +649,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/24 12:14:27</t>
+          <t>07/27 12:33:27</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>14706</t>
+          <t>34939</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -661,12 +676,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/24 10:07:46</t>
+          <t>07/24 12:14:27</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>14706</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -676,7 +691,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -688,12 +703,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/23 12:17:40</t>
+          <t>07/24 10:07:46</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>78900</t>
+          <t>588</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -703,7 +718,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -715,12 +730,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/22 14:19:28</t>
+          <t>07/23 12:17:40</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>78900</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -742,12 +757,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/20 15:05:00</t>
+          <t>07/22 14:19:28</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -769,12 +784,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/20 14:00:54</t>
+          <t>07/20 15:05:00</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>6754</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -796,12 +811,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/17 17:15:59</t>
+          <t>07/20 14:00:54</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -823,83 +838,110 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>07/17 17:15:59</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>11976</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>07/15 18:20:02</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>13173</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2060000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>248307.31</t>
+          <t>2210000</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>248303</t>
+          <t>266271.39</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>248303</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>4.31</t>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>17968.39</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
+++ b/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
@@ -622,12 +622,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/31 16:18:51</t>
+          <t>07/31 21:14:26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>62783</t>
+          <t>17964</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -649,12 +649,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/27 12:33:27</t>
+          <t>07/31 16:18:51</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>34939</t>
+          <t>62783</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -676,12 +676,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/24 12:14:27</t>
+          <t>07/27 12:33:27</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14706</t>
+          <t>34939</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -703,12 +703,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/24 10:07:46</t>
+          <t>07/24 12:14:27</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>14706</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -730,12 +730,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/23 12:17:40</t>
+          <t>07/24 10:07:46</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>78900</t>
+          <t>588</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -757,12 +757,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/22 14:19:28</t>
+          <t>07/23 12:17:40</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>78900</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -784,12 +784,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/20 15:05:00</t>
+          <t>07/22 14:19:28</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -811,12 +811,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/20 14:00:54</t>
+          <t>07/20 15:05:00</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>6754</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -838,12 +838,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/17 17:15:59</t>
+          <t>07/20 14:00:54</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -865,83 +865,110 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>07/17 17:15:59</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>11976</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>07/15 18:20:02</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>13173</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2210000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>266271.39</t>
+          <t>2210000</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>248303</t>
+          <t>266271.39</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>266267</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>17968.39</t>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>4.39</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
+++ b/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/31 20:06:51</t>
+          <t>08/04 15:44:42</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>17964.07</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/31 14:56:13</t>
+          <t>07/31 20:06:51</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>350000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>42424.24</t>
+          <t>17964.07</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/31 14:44:37</t>
+          <t>07/31 14:56:13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>350000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20359.28</t>
+          <t>42424.24</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/27 10:22:47</t>
+          <t>07/31 14:44:37</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>290000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>34939.76</t>
+          <t>20359.28</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/24 10:07:41</t>
+          <t>07/27 10:22:47</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>290000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>15294.12</t>
+          <t>34939.76</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/23 10:46:53</t>
+          <t>07/24 10:07:41</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>15294.12</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/23 10:05:11</t>
+          <t>07/23 10:46:53</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>48780.49</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/22 10:21:23</t>
+          <t>07/23 10:05:11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>48780.49</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/20 14:00:36</t>
+          <t>07/22 10:21:23</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>7142.86</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/17 15:25:54</t>
+          <t>07/20 14:00:36</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>11976.05</t>
+          <t>7142.86</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,166 +495,181 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>07/17 15:25:54</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>8.35</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>11976.05</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>07/15 16:22:47</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>110000</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>8.35</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>13173.65</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
+      <c r="F16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/31 21:14:26</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>17964</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/31 16:18:51</t>
+          <t>07/31 21:14:26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>62783</t>
+          <t>17964</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -664,7 +679,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -676,12 +691,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/27 12:33:27</t>
+          <t>07/31 16:18:51</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>34939</t>
+          <t>62783</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -691,7 +706,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -703,12 +718,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/24 12:14:27</t>
+          <t>07/27 12:33:27</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>14706</t>
+          <t>34939</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -730,12 +745,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/24 10:07:46</t>
+          <t>07/24 12:14:27</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>14706</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -745,7 +760,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -757,12 +772,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/23 12:17:40</t>
+          <t>07/24 10:07:46</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>78900</t>
+          <t>588</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -772,7 +787,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -784,12 +799,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/22 14:19:28</t>
+          <t>07/23 12:17:40</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>78900</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -811,12 +826,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/20 15:05:00</t>
+          <t>07/22 14:19:28</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -838,12 +853,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/20 14:00:54</t>
+          <t>07/20 15:05:00</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>6754</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -865,12 +880,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/17 17:15:59</t>
+          <t>07/20 14:00:54</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -892,83 +907,110 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>07/17 17:15:59</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>11976</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>07/15 18:20:02</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>13173</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2210000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>266271.39</t>
+          <t>2310000</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>266267</t>
+          <t>278319.58</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>266267</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>4.39</t>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>12052.58</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
+++ b/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
@@ -664,12 +664,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/31 21:14:26</t>
+          <t>08/04 17:00:59</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>17964</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -691,12 +691,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/31 16:18:51</t>
+          <t>07/31 21:14:26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>62783</t>
+          <t>17964</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -718,12 +718,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/27 12:33:27</t>
+          <t>07/31 16:18:51</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>34939</t>
+          <t>62783</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -745,12 +745,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/24 12:14:27</t>
+          <t>07/27 12:33:27</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>14706</t>
+          <t>34939</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -772,12 +772,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/24 10:07:46</t>
+          <t>07/24 12:14:27</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>14706</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -799,12 +799,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/23 12:17:40</t>
+          <t>07/24 10:07:46</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>78900</t>
+          <t>588</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -826,12 +826,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/22 14:19:28</t>
+          <t>07/23 12:17:40</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>78900</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -853,12 +853,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/20 15:05:00</t>
+          <t>07/22 14:19:28</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -880,12 +880,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/20 14:00:54</t>
+          <t>07/20 15:05:00</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>6754</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -907,12 +907,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/17 17:15:59</t>
+          <t>07/20 14:00:54</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -934,83 +934,110 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>07/17 17:15:59</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>11976</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>07/15 18:20:02</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>13173</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="34"/>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2310000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>278319.58</t>
+          <t>2310000</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>266267</t>
+          <t>278319.58</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>278315</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>12052.58</t>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>4.58</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
+++ b/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/04 15:44:42</t>
+          <t>08/07 10:14:10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>36585.37</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/31 20:06:51</t>
+          <t>08/04 15:44:42</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>17964.07</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/31 14:56:13</t>
+          <t>07/31 20:06:51</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>350000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>42424.24</t>
+          <t>17964.07</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/31 14:44:37</t>
+          <t>07/31 14:56:13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>350000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>20359.28</t>
+          <t>42424.24</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/27 10:22:47</t>
+          <t>07/31 14:44:37</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>290000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>34939.76</t>
+          <t>20359.28</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/24 10:07:41</t>
+          <t>07/27 10:22:47</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>290000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>15294.12</t>
+          <t>34939.76</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/23 10:46:53</t>
+          <t>07/24 10:07:41</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>15294.12</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/23 10:05:11</t>
+          <t>07/23 10:46:53</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>48780.49</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/22 10:21:23</t>
+          <t>07/23 10:05:11</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>48780.49</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/20 14:00:36</t>
+          <t>07/22 10:21:23</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>7142.86</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/17 15:25:54</t>
+          <t>07/20 14:00:36</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>11976.05</t>
+          <t>7142.86</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,166 +537,181 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>07/17 15:25:54</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>8.35</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>11976.05</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>07/15 16:22:47</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>110000</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>8.35</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>13173.65</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
+      <c r="F17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08/04 17:00:59</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/31 21:14:26</t>
+          <t>08/04 17:00:59</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>17964</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -718,12 +733,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/31 16:18:51</t>
+          <t>07/31 21:14:26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>62783</t>
+          <t>17964</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -733,7 +748,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -745,12 +760,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/27 12:33:27</t>
+          <t>07/31 16:18:51</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>34939</t>
+          <t>62783</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -760,7 +775,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -772,12 +787,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/24 12:14:27</t>
+          <t>07/27 12:33:27</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>14706</t>
+          <t>34939</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -799,12 +814,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/24 10:07:46</t>
+          <t>07/24 12:14:27</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>14706</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -814,7 +829,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -826,12 +841,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/23 12:17:40</t>
+          <t>07/24 10:07:46</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>78900</t>
+          <t>588</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -841,7 +856,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -853,12 +868,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/22 14:19:28</t>
+          <t>07/23 12:17:40</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>78900</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -880,12 +895,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/20 15:05:00</t>
+          <t>07/22 14:19:28</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -907,12 +922,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/20 14:00:54</t>
+          <t>07/20 15:05:00</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>6754</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -934,12 +949,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/17 17:15:59</t>
+          <t>07/20 14:00:54</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -961,83 +976,110 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>07/17 17:15:59</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>11976</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>07/15 18:20:02</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>13173</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="36"/>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2310000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>278319.58</t>
+          <t>2610000</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>278315</t>
+          <t>314904.94</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>278315</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>4.58</t>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>36589.94</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
+++ b/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
@@ -706,12 +706,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08/04 17:00:59</t>
+          <t>08/07 11:38:09</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>36585</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -733,12 +733,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/31 21:14:26</t>
+          <t>08/04 17:00:59</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>17964</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -760,12 +760,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/31 16:18:51</t>
+          <t>07/31 21:14:26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>62783</t>
+          <t>17964</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -787,12 +787,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/27 12:33:27</t>
+          <t>07/31 16:18:51</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>34939</t>
+          <t>62783</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -814,12 +814,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/24 12:14:27</t>
+          <t>07/27 12:33:27</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>14706</t>
+          <t>34939</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -841,12 +841,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/24 10:07:46</t>
+          <t>07/24 12:14:27</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>14706</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -868,12 +868,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/23 12:17:40</t>
+          <t>07/24 10:07:46</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>78900</t>
+          <t>588</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -895,12 +895,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/22 14:19:28</t>
+          <t>07/23 12:17:40</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>78900</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -922,12 +922,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/20 15:05:00</t>
+          <t>07/22 14:19:28</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -949,12 +949,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/20 14:00:54</t>
+          <t>07/20 15:05:00</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>6754</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -976,12 +976,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/17 17:15:59</t>
+          <t>07/20 14:00:54</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1003,83 +1003,110 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>07/17 17:15:59</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>11976</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>07/15 18:20:02</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>13173</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="36"/>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2610000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>314904.94</t>
+          <t>2610000</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>278315</t>
+          <t>314904.94</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>314900</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>36589.94</t>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>4.94</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
+++ b/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/07 10:14:10</t>
+          <t>08/07 20:48:26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>36585.37</t>
+          <t>30487.8</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/04 15:44:42</t>
+          <t>08/07 10:14:10</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>36585.37</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/31 20:06:51</t>
+          <t>08/04 15:44:42</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>17964.07</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/31 14:56:13</t>
+          <t>07/31 20:06:51</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>350000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>42424.24</t>
+          <t>17964.07</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/31 14:44:37</t>
+          <t>07/31 14:56:13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>350000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>20359.28</t>
+          <t>42424.24</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/27 10:22:47</t>
+          <t>07/31 14:44:37</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>290000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>34939.76</t>
+          <t>20359.28</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/24 10:07:41</t>
+          <t>07/27 10:22:47</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>290000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>15294.12</t>
+          <t>34939.76</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/23 10:46:53</t>
+          <t>07/24 10:07:41</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>15294.12</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/23 10:05:11</t>
+          <t>07/23 10:46:53</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>48780.49</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/22 10:21:23</t>
+          <t>07/23 10:05:11</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>48780.49</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/20 14:00:36</t>
+          <t>07/22 10:21:23</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>7142.86</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/17 15:25:54</t>
+          <t>07/20 14:00:36</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>11976.05</t>
+          <t>7142.86</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,166 +579,181 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>07/17 15:25:54</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>8.35</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>11976.05</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>07/15 16:22:47</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>110000</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>8.35</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>13173.65</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
+      <c r="F18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08/07 11:38:09</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>36585</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08/04 17:00:59</t>
+          <t>08/07 11:38:09</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>36585</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -760,12 +775,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/31 21:14:26</t>
+          <t>08/04 17:00:59</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>17964</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -787,12 +802,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/31 16:18:51</t>
+          <t>07/31 21:14:26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>62783</t>
+          <t>17964</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -802,7 +817,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -814,12 +829,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/27 12:33:27</t>
+          <t>07/31 16:18:51</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>34939</t>
+          <t>62783</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -829,7 +844,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -841,12 +856,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/24 12:14:27</t>
+          <t>07/27 12:33:27</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>14706</t>
+          <t>34939</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -868,12 +883,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/24 10:07:46</t>
+          <t>07/24 12:14:27</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>14706</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -883,7 +898,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -895,12 +910,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/23 12:17:40</t>
+          <t>07/24 10:07:46</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>78900</t>
+          <t>588</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -910,7 +925,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -922,12 +937,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/22 14:19:28</t>
+          <t>07/23 12:17:40</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>78900</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -949,12 +964,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/20 15:05:00</t>
+          <t>07/22 14:19:28</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -976,12 +991,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/20 14:00:54</t>
+          <t>07/20 15:05:00</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>6754</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1003,12 +1018,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/17 17:15:59</t>
+          <t>07/20 14:00:54</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1030,83 +1045,110 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>07/17 17:15:59</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>11976</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>07/15 18:20:02</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>13173</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="37"/>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="38"/>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2610000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>314904.94</t>
+          <t>2860000</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>314900</t>
+          <t>345392.75</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>314900</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>4.94</t>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>30492.75</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
+++ b/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
@@ -748,12 +748,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08/07 11:38:09</t>
+          <t>08/07 21:54:08</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>36585</t>
+          <t>30488</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -775,12 +775,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08/04 17:00:59</t>
+          <t>08/07 11:38:09</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>36585</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -802,12 +802,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/31 21:14:26</t>
+          <t>08/04 17:00:59</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>17964</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -829,12 +829,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/31 16:18:51</t>
+          <t>07/31 21:14:26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>62783</t>
+          <t>17964</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -856,12 +856,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/27 12:33:27</t>
+          <t>07/31 16:18:51</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>34939</t>
+          <t>62783</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -883,12 +883,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/24 12:14:27</t>
+          <t>07/27 12:33:27</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>14706</t>
+          <t>34939</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -910,12 +910,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/24 10:07:46</t>
+          <t>07/24 12:14:27</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>14706</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -925,7 +925,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -937,12 +937,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/23 12:17:40</t>
+          <t>07/24 10:07:46</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>78900</t>
+          <t>588</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -964,12 +964,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/22 14:19:28</t>
+          <t>07/23 12:17:40</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>78900</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -991,12 +991,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/20 15:05:00</t>
+          <t>07/22 14:19:28</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1018,12 +1018,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/20 14:00:54</t>
+          <t>07/20 15:05:00</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>6754</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1045,12 +1045,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/17 17:15:59</t>
+          <t>07/20 14:00:54</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1072,83 +1072,110 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>07/17 17:15:59</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>11976</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>07/15 18:20:02</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>13173</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="38"/>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2860000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>345392.75</t>
+          <t>2860000</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>314900</t>
+          <t>345392.75</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>345388</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>30492.75</t>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>4.75</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
+++ b/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/07 20:48:26</t>
+          <t>08/09 20:11:27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>82993</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>30487.8</t>
+          <t>9431.02</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/07 10:14:10</t>
+          <t>08/07 20:48:26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>36585.37</t>
+          <t>30487.8</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/04 15:44:42</t>
+          <t>08/07 10:14:10</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>36585.37</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/31 20:06:51</t>
+          <t>08/04 15:44:42</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>17964.07</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/31 14:56:13</t>
+          <t>07/31 20:06:51</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>350000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>42424.24</t>
+          <t>17964.07</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/31 14:44:37</t>
+          <t>07/31 14:56:13</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>350000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>20359.28</t>
+          <t>42424.24</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/27 10:22:47</t>
+          <t>07/31 14:44:37</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>290000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>34939.76</t>
+          <t>20359.28</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/24 10:07:41</t>
+          <t>07/27 10:22:47</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>290000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>15294.12</t>
+          <t>34939.76</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/23 10:46:53</t>
+          <t>07/24 10:07:41</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>15294.12</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/23 10:05:11</t>
+          <t>07/23 10:46:53</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>48780.49</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/22 10:21:23</t>
+          <t>07/23 10:05:11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>48780.49</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/20 14:00:36</t>
+          <t>07/22 10:21:23</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>7142.86</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/17 15:25:54</t>
+          <t>07/20 14:00:36</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>11976.05</t>
+          <t>7142.86</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,166 +621,181 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>07/17 15:25:54</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>8.35</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>11976.05</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>07/15 16:22:47</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>110000</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>8.35</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>13173.65</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
+      <c r="F19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08/07 21:54:08</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>30488</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08/07 11:38:09</t>
+          <t>08/07 21:54:08</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>36585</t>
+          <t>30488</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -802,12 +817,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08/04 17:00:59</t>
+          <t>08/07 11:38:09</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>36585</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -829,12 +844,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/31 21:14:26</t>
+          <t>08/04 17:00:59</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>17964</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -856,12 +871,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/31 16:18:51</t>
+          <t>07/31 21:14:26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>62783</t>
+          <t>17964</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -871,7 +886,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -883,12 +898,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/27 12:33:27</t>
+          <t>07/31 16:18:51</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>34939</t>
+          <t>62783</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -898,7 +913,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -910,12 +925,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/24 12:14:27</t>
+          <t>07/27 12:33:27</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>14706</t>
+          <t>34939</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -937,12 +952,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/24 10:07:46</t>
+          <t>07/24 12:14:27</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>14706</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -952,7 +967,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -964,12 +979,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/23 12:17:40</t>
+          <t>07/24 10:07:46</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>78900</t>
+          <t>588</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -979,7 +994,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -991,12 +1006,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/22 14:19:28</t>
+          <t>07/23 12:17:40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>78900</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1018,12 +1033,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/20 15:05:00</t>
+          <t>07/22 14:19:28</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1045,12 +1060,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/20 14:00:54</t>
+          <t>07/20 15:05:00</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>6754</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1072,12 +1087,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/17 17:15:59</t>
+          <t>07/20 14:00:54</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1099,83 +1114,110 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>07/17 17:15:59</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>11976</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>07/15 18:20:02</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>13173</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="39"/>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2860000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>345392.75</t>
+          <t>2942993</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>345388</t>
+          <t>354823.77</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>345388</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>4.75</t>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>9435.77</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
+++ b/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/09 20:11:27</t>
+          <t>08/09 20:11:43</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>82993</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>9431.02</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/07 20:48:26</t>
+          <t>08/09 20:11:27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>82993</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>30487.8</t>
+          <t>9431.02</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/07 10:14:10</t>
+          <t>08/07 20:48:26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>36585.37</t>
+          <t>30487.8</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/04 15:44:42</t>
+          <t>08/07 10:14:10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>36585.37</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/31 20:06:51</t>
+          <t>08/04 15:44:42</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>17964.07</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/31 14:56:13</t>
+          <t>07/31 20:06:51</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>350000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>42424.24</t>
+          <t>17964.07</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/31 14:44:37</t>
+          <t>07/31 14:56:13</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>350000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>20359.28</t>
+          <t>42424.24</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/27 10:22:47</t>
+          <t>07/31 14:44:37</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>290000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>34939.76</t>
+          <t>20359.28</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/24 10:07:41</t>
+          <t>07/27 10:22:47</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>290000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>15294.12</t>
+          <t>34939.76</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/23 10:46:53</t>
+          <t>07/24 10:07:41</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>15294.12</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/23 10:05:11</t>
+          <t>07/23 10:46:53</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>48780.49</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/22 10:21:23</t>
+          <t>07/23 10:05:11</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>48780.49</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/20 14:00:36</t>
+          <t>07/22 10:21:23</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>7142.86</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/17 15:25:54</t>
+          <t>07/20 14:00:36</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>11976.05</t>
+          <t>7142.86</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,166 +663,181 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>07/17 15:25:54</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>8.35</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>11976.05</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>07/15 16:22:47</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>110000</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>8.35</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>13173.65</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
+      <c r="F20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08/07 21:54:08</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>30488</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08/07 11:38:09</t>
+          <t>08/07 21:54:08</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>36585</t>
+          <t>30488</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -844,12 +859,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08/04 17:00:59</t>
+          <t>08/07 11:38:09</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>36585</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -871,12 +886,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/31 21:14:26</t>
+          <t>08/04 17:00:59</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>17964</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -898,12 +913,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/31 16:18:51</t>
+          <t>07/31 21:14:26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>62783</t>
+          <t>17964</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -913,7 +928,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -925,12 +940,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/27 12:33:27</t>
+          <t>07/31 16:18:51</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>34939</t>
+          <t>62783</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -940,7 +955,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -952,12 +967,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/24 12:14:27</t>
+          <t>07/27 12:33:27</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>14706</t>
+          <t>34939</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -979,12 +994,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/24 10:07:46</t>
+          <t>07/24 12:14:27</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>14706</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -994,7 +1009,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1006,12 +1021,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/23 12:17:40</t>
+          <t>07/24 10:07:46</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>78900</t>
+          <t>588</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1021,7 +1036,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1033,12 +1048,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/22 14:19:28</t>
+          <t>07/23 12:17:40</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>78900</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1060,12 +1075,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/20 15:05:00</t>
+          <t>07/22 14:19:28</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1087,12 +1102,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/20 14:00:54</t>
+          <t>07/20 15:05:00</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>6754</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1114,12 +1129,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/17 17:15:59</t>
+          <t>07/20 14:00:54</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1141,83 +1156,110 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>07/17 17:15:59</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>11976</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>07/15 18:20:02</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>13173</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="40"/>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="41"/>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2942993</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>354823.77</t>
+          <t>3042993</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>345388</t>
+          <t>366871.96</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>345388</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>9435.77</t>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>21483.96</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
+++ b/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
@@ -832,12 +832,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08/07 21:54:08</t>
+          <t>08/09 21:47:23</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>30488</t>
+          <t>21419</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -859,12 +859,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08/07 11:38:09</t>
+          <t>08/07 21:54:08</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>36585</t>
+          <t>30488</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -886,12 +886,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08/04 17:00:59</t>
+          <t>08/07 11:38:09</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>36585</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -913,12 +913,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/31 21:14:26</t>
+          <t>08/04 17:00:59</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>17964</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -940,12 +940,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/31 16:18:51</t>
+          <t>07/31 21:14:26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>62783</t>
+          <t>17964</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -967,12 +967,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/27 12:33:27</t>
+          <t>07/31 16:18:51</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>34939</t>
+          <t>62783</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -994,12 +994,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/24 12:14:27</t>
+          <t>07/27 12:33:27</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>14706</t>
+          <t>34939</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1021,12 +1021,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/24 10:07:46</t>
+          <t>07/24 12:14:27</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>14706</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1048,12 +1048,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/23 12:17:40</t>
+          <t>07/24 10:07:46</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>78900</t>
+          <t>588</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1075,12 +1075,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/22 14:19:28</t>
+          <t>07/23 12:17:40</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>78900</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1102,12 +1102,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/20 15:05:00</t>
+          <t>07/22 14:19:28</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1129,12 +1129,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/20 14:00:54</t>
+          <t>07/20 15:05:00</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>6754</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1156,12 +1156,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/17 17:15:59</t>
+          <t>07/20 14:00:54</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1183,83 +1183,110 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>07/17 17:15:59</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>11976</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>07/15 18:20:02</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>13173</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="41"/>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>3042993</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>366871.96</t>
+          <t>3042993</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>345388</t>
+          <t>366871.96</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>366807</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>21483.96</t>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>64.96</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
+++ b/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
@@ -832,12 +832,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08/09 21:47:23</t>
+          <t>08/09 21:50:22</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>21419</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -859,12 +859,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08/07 21:54:08</t>
+          <t>08/09 21:47:23</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>30488</t>
+          <t>21419</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -886,12 +886,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08/07 11:38:09</t>
+          <t>08/07 21:54:08</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>36585</t>
+          <t>30488</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -913,12 +913,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08/04 17:00:59</t>
+          <t>08/07 11:38:09</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>36585</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -940,12 +940,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/31 21:14:26</t>
+          <t>08/04 17:00:59</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>17964</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -967,12 +967,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/31 16:18:51</t>
+          <t>07/31 21:14:26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>62783</t>
+          <t>17964</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -994,12 +994,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/27 12:33:27</t>
+          <t>07/31 16:18:51</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>34939</t>
+          <t>62783</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1021,12 +1021,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/24 12:14:27</t>
+          <t>07/27 12:33:27</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>14706</t>
+          <t>34939</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1048,12 +1048,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/24 10:07:46</t>
+          <t>07/24 12:14:27</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>14706</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1075,12 +1075,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/23 12:17:40</t>
+          <t>07/24 10:07:46</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>78900</t>
+          <t>588</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1102,12 +1102,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/22 14:19:28</t>
+          <t>07/23 12:17:40</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>78900</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1129,12 +1129,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/20 15:05:00</t>
+          <t>07/22 14:19:28</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1156,12 +1156,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/20 14:00:54</t>
+          <t>07/20 15:05:00</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>6754</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1183,12 +1183,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/17 17:15:59</t>
+          <t>07/20 14:00:54</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1210,83 +1210,110 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>07/17 17:15:59</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>11976</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>07/15 18:20:02</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>13173</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="42"/>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="43"/>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>3042993</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>366871.96</t>
+          <t>3042993</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>366807</t>
+          <t>366871.96</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>366867</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>64.96</t>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>4.96</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
+++ b/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/09 20:11:43</t>
+          <t>08/10 14:51:39</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1020000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>125925.93</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/09 20:11:27</t>
+          <t>08/09 20:11:43</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>82993</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>9431.02</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/07 20:48:26</t>
+          <t>08/09 20:11:27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>82993</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>30487.8</t>
+          <t>9431.02</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/07 10:14:10</t>
+          <t>08/07 20:48:26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>36585.37</t>
+          <t>30487.8</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/04 15:44:42</t>
+          <t>08/07 10:14:10</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>36585.37</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/31 20:06:51</t>
+          <t>08/04 15:44:42</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>17964.07</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/31 14:56:13</t>
+          <t>07/31 20:06:51</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>350000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>42424.24</t>
+          <t>17964.07</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/31 14:44:37</t>
+          <t>07/31 14:56:13</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>350000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>20359.28</t>
+          <t>42424.24</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/27 10:22:47</t>
+          <t>07/31 14:44:37</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>290000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>34939.76</t>
+          <t>20359.28</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/24 10:07:41</t>
+          <t>07/27 10:22:47</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>290000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>15294.12</t>
+          <t>34939.76</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/23 10:46:53</t>
+          <t>07/24 10:07:41</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>15294.12</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/23 10:05:11</t>
+          <t>07/23 10:46:53</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>48780.49</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/22 10:21:23</t>
+          <t>07/23 10:05:11</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>48780.49</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/20 14:00:36</t>
+          <t>07/22 10:21:23</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>7142.86</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/17 15:25:54</t>
+          <t>07/20 14:00:36</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>11976.05</t>
+          <t>7142.86</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,166 +705,181 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>07/17 15:25:54</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>8.35</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>11976.05</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>07/15 16:22:47</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>110000</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>8.35</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>13173.65</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
+      <c r="F21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08/09 21:50:22</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08/09 21:47:23</t>
+          <t>08/09 21:50:22</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>21419</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -886,12 +901,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08/07 21:54:08</t>
+          <t>08/09 21:47:23</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>30488</t>
+          <t>21419</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -913,12 +928,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08/07 11:38:09</t>
+          <t>08/07 21:54:08</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>36585</t>
+          <t>30488</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -940,12 +955,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08/04 17:00:59</t>
+          <t>08/07 11:38:09</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>36585</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -967,12 +982,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/31 21:14:26</t>
+          <t>08/04 17:00:59</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>17964</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -994,12 +1009,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/31 16:18:51</t>
+          <t>07/31 21:14:26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>62783</t>
+          <t>17964</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1009,7 +1024,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1021,12 +1036,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/27 12:33:27</t>
+          <t>07/31 16:18:51</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>34939</t>
+          <t>62783</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1036,7 +1051,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1048,12 +1063,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/24 12:14:27</t>
+          <t>07/27 12:33:27</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>14706</t>
+          <t>34939</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1075,12 +1090,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/24 10:07:46</t>
+          <t>07/24 12:14:27</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>14706</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1090,7 +1105,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1102,12 +1117,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/23 12:17:40</t>
+          <t>07/24 10:07:46</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>78900</t>
+          <t>588</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1117,7 +1132,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1129,12 +1144,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/22 14:19:28</t>
+          <t>07/23 12:17:40</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>78900</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1156,12 +1171,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/20 15:05:00</t>
+          <t>07/22 14:19:28</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1183,12 +1198,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/20 14:00:54</t>
+          <t>07/20 15:05:00</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>6754</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1210,12 +1225,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/17 17:15:59</t>
+          <t>07/20 14:00:54</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1237,83 +1252,110 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>07/17 17:15:59</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>11976</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>07/15 18:20:02</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>13173</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="43"/>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="44"/>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>3042993</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>366871.96</t>
+          <t>4062993</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>366867</t>
+          <t>492797.89</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>366867</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>4.96</t>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>125930.89</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
+++ b/bills/JXZFSP/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-all.xlsx
@@ -874,12 +874,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08/09 21:50:22</t>
+          <t>08/10 16:20:58</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>125925</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -901,12 +901,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08/09 21:47:23</t>
+          <t>08/09 21:50:22</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>21419</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -928,12 +928,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08/07 21:54:08</t>
+          <t>08/09 21:47:23</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>30488</t>
+          <t>21419</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -955,12 +955,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08/07 11:38:09</t>
+          <t>08/07 21:54:08</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>36585</t>
+          <t>30488</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -982,12 +982,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08/04 17:00:59</t>
+          <t>08/07 11:38:09</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>36585</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1009,12 +1009,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/31 21:14:26</t>
+          <t>08/04 17:00:59</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>17964</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1036,12 +1036,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/31 16:18:51</t>
+          <t>07/31 21:14:26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>62783</t>
+          <t>17964</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1063,12 +1063,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/27 12:33:27</t>
+          <t>07/31 16:18:51</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>34939</t>
+          <t>62783</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1090,12 +1090,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/24 12:14:27</t>
+          <t>07/27 12:33:27</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>14706</t>
+          <t>34939</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1117,12 +1117,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/24 10:07:46</t>
+          <t>07/24 12:14:27</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>14706</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1144,12 +1144,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/23 12:17:40</t>
+          <t>07/24 10:07:46</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>78900</t>
+          <t>588</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1171,12 +1171,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/22 14:19:28</t>
+          <t>07/23 12:17:40</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>78900</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1198,12 +1198,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/20 15:05:00</t>
+          <t>07/22 14:19:28</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1225,12 +1225,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/20 14:00:54</t>
+          <t>07/20 15:05:00</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>6754</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1252,12 +1252,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/17 17:15:59</t>
+          <t>07/20 14:00:54</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1279,83 +1279,110 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>07/17 17:15:59</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>11976</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>07/15 18:20:02</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>13173</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="44"/>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="45"/>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>4062993</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>492797.89</t>
+          <t>4062993</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>366867</t>
+          <t>492797.89</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>492792</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>125930.89</t>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>5.89</t>
         </is>
       </c>
     </row>
